--- a/sports_forms/023_spring_tennis_challenge_registration_form--sports_forms.xlsx
+++ b/sports_forms/023_spring_tennis_challenge_registration_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,64 +566,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_phone</t>
+          <t>challenge_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Participant Phone</t>
+          <t>Challenge Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>challenge_name</t>
+          <t>challenge_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Challenge Name</t>
+          <t>Challenge Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>challenge_date</t>
+          <t>challenge_start_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Challenge Date</t>
+          <t>Challenge Start Time</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>challenge_start_time</t>
+          <t>challenge_end_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Challenge Start Time</t>
+          <t>Challenge End Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>challenge_end_time</t>
+          <t>participant_formation_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Challenge End Time</t>
+          <t>Participant Formation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>participant_formation</t>
+          <t>participant_formation_size</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Participant Formation</t>
+          <t>Team Size</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,386 +704,87 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>participant_tennis_experience</t>
+          <t>participant_formation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Participant Tennis Experience</t>
+          <t>Team Members</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>participant_gender</t>
+          <t>participant_experience</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Participant Gender</t>
+          <t>Participant Tennis Experience</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_age</t>
+          <t>participant_gender</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Participant Age</t>
+          <t>Participant Gender</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>participant_formation</t>
+          <t>participant_age</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Participant Formation</t>
+          <t>Participant Age</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Team Size</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Team Members</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Team Name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Participant Formation</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Team Members</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Singles</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Doubles</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Mixed Doubles</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Team Player</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Team Size</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_formation</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,272 +827,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>participant_formation_choices</t>
+          <t>participant_formation_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single_player',_'value':_'single_player'}</t>
+          <t>single_player</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Single Player', 'value': 'Single Player'}</t>
+          <t>Single Player</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>participant_formation_choices</t>
+          <t>participant_formation_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'team_player',_'value':_'team_player'}</t>
+          <t>team_player</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Team Player', 'value': 'Team Player'}</t>
+          <t>Team Player</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>participant_tennis_experience_choices</t>
+          <t>participant_formation_size_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'beginner',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Beginner', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>participant_tennis_experience_choices</t>
+          <t>participant_formation_size_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'intermediate',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Intermediate', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>participant_tennis_experience_choices</t>
+          <t>participant_formation_size_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'advanced',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Advanced', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>participant_gender_choices</t>
+          <t>participant_formation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'male',_'value':_'male'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Male', 'value': 'Male'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>participant_gender_choices</t>
+          <t>participant_formation_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'female',_'value':_'female'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Female', 'value': 'Female'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>participant_gender_choices</t>
+          <t>participant_formation_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>participant_formation_choices</t>
+          <t>participant_experience_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single_player',_'value':_'single_player'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Single Player', 'value': 'Single Player'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>participant_formation_choices</t>
+          <t>participant_experience_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'team_player',_'value':_'team_player'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Team Player', 'value': 'Team Player'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>participant_formation_choices</t>
+          <t>participant_experience_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'singles',_'value':_1}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Singles', 'value': 1}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>participant_formation_choices</t>
+          <t>participant_gender_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'doubles',_'value':_2}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Doubles', 'value': 2}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>participant_formation_choices</t>
+          <t>participant_gender_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mixed_doubles',_'value':_3}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mixed Doubles', 'value': 3}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>participant_formation_choices</t>
+          <t>participant_gender_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john_doe',_'value':_'john_doe'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John Doe', 'value': 'John Doe'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>participant_formation_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'jane_doe',_'value':_'jane_doe'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Jane Doe', 'value': 'Jane Doe'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>participant_formation_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'jim',_'value':_'jim'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Jim', 'value': 'Jim'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
